--- a/Docs/data_dictionary.xlsx
+++ b/Docs/data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/387f7955a8677bf5/Desktop/Springer-referral-pipeline/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_7725862E13DC463B2DC2C3F0505ED87656CD16B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CA62B4F-76E8-4111-B702-479288CA5B0C}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_7725862E13DC463B2DC2C3F0505ED87656CD16B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E170640B-EDDC-4EC4-A0A9-78035A8BD98D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3130" yWindow="1140" windowWidth="14400" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Output Report" sheetId="1" r:id="rId1"/>
@@ -317,7 +317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,16 +325,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -342,13 +362,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -366,6 +410,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,471 +704,472 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="1" max="1" width="23.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="84.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="65.453125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="47" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E18" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="A19" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="A20" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="A22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="E22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="58" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+    <row r="23" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
         <v>96</v>
       </c>
     </row>
